--- a/public/sap-reporting/expansion-150-downloads/EXT-CO26-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO26-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1391b7bb84d14eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rbc7f62b7da8142c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1f0f2ddff0164211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R0e8030362b4b4943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R81827d8332f44041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R4dfbef151d5144d8"/>
   </x:sheets>
 </x:workbook>
 </file>
